--- a/backend/src/evolve/Kelsic_Data_foldy/Round_4_top_variants.xlsx
+++ b/backend/src/evolve/Kelsic_Data_foldy/Round_4_top_variants.xlsx
@@ -443,121 +443,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D5L</t>
+          <t>V31N</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.0235</v>
+        <v>1.015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E4I</t>
+          <t>V31A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.015666666666666</v>
+        <v>1.01325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E4Y</t>
+          <t>T54S</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.017</v>
+        <v>0.9768333333333334</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E4L</t>
+          <t>V31M</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9845</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E4M</t>
+          <t>V53C</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.008</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E4V</t>
+          <t>V68S</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9977499999999999</v>
+        <v>0.9561666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E4A</t>
+          <t>V68N</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.853</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E15N</t>
+          <t>V31F</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9624999999999999</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T12L</t>
+          <t>V31Q</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9253333333333332</v>
+        <v>1.0025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G29A</t>
+          <t>A34G</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9904999999999999</v>
+        <v>1.01275</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T33N</t>
+          <t>V53P</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.0095</v>
+        <v>0.47475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E8K</t>
+          <t>V32A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9385</v>
+        <v>0.922</v>
       </c>
     </row>
   </sheetData>

--- a/backend/src/evolve/Kelsic_Data_foldy/Round_4_top_variants.xlsx
+++ b/backend/src/evolve/Kelsic_Data_foldy/Round_4_top_variants.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,121 +443,991 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V31N</t>
+          <t>A2Y</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.015</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V31A</t>
+          <t>H35M</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.01325</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T54S</t>
+          <t>E4H</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9768333333333334</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V31M</t>
+          <t>V32I</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.998</v>
+        <v>1.003333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V53C</t>
+          <t>S71R</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.949</v>
+        <v>0.9955000000000002</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V68S</t>
+          <t>M21R</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9561666666666667</v>
+        <v>0.9923333333333334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V68N</t>
+          <t>L62H</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.948</v>
+        <v>0.9664999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V31F</t>
+          <t>H35F</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.007</v>
+        <v>1.0305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V31Q</t>
+          <t>L62K</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.0025</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A34G</t>
+          <t>V68R</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.01275</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V53P</t>
+          <t>E4N</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.47475</v>
+        <v>1.0115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V32A</t>
+          <t>T16K</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.922</v>
+        <v>1.045</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M40F</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.358</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A2E</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.013</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I7H</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9835</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D5C</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.0095</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E56K</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9744999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D5R</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.8489999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>V31S</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.009166666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T16C</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9884999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R23L</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.004833333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H35I</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9873333333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S63H</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T58H</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9305000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D61H</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.9255</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L62A</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.9512499999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>N6R</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.8531666666666665</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P59E</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.9245</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T49L</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.9169999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>N6Y</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.005</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q10T</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.92725</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>K42H</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.917</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>K3H</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.721</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H35W</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.978</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>V32C</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>I67V</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.9692499999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P59W</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>V24I</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.9906666666666667</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>V68H</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.9415</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S37K</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.9425</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R23N</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.903</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>I47F</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.4765</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>E27Y</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.8294999999999999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>R46H</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.7875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Y60F</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>N28S</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.846</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T16P</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.9672500000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>V31N</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.015</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T20Q</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.971</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>N43T</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P18E</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.528</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>I7R</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.8526666666666666</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>E15V</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.93775</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T16R</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.9976666666666668</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>H30W</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>M40V</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.93025</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>V31H</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.0085</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>R23I</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.007666666666666</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>E4W</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.666</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P18M</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.981</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S37M</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.842</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>D5W</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.873</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>R66K</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.881</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L62S</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.9543333333333334</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>E8G</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.7705</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>G50H</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.9015</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>E27W</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.776</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>I7T</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.882</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>V55F</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>I47C</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S63P</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.65125</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L48Y</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.9005000000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>V13A</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A34C</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>V68C</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.9664999999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L62F</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.9664999999999999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>E15G</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.97175</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>I7Q</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>V31I</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1.004333333333333</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>E27L</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.8439999999999999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>E56R</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.9636666666666666</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>L62W</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A2D</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1.0375</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T20C</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P18T</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.9722499999999999</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>I7S</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.9325000000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>I7A</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.82275</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S63G</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.84875</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Y60W</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>L62G</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.9452499999999999</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T33E</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.9715</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L48F</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.917</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>H30G</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.9825</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>V32F</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.9655</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>D61S</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.9621666666666666</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L14K</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.959</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>K3F</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.905</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Q10Y</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.9595</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>T54K</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.9339999999999999</v>
       </c>
     </row>
   </sheetData>
